--- a/terminology/ValueSet-allergy-intolerance-category-cz.xlsx
+++ b/terminology/ValueSet-allergy-intolerance-category-cz.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Allergy Intolerance Category (CZ supplement)</t>
+    <t>Allergy Intolerance Category (CZ supplement value set)</t>
   </si>
   <si>
     <t>Status</t>
